--- a/data/trans_orig/P1431-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2012</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682717</t>
+          <t>683125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>696480</t>
+          <t>697265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677753</t>
+          <t>678672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>691166</t>
+          <t>691140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1365679</t>
+          <t>1366126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1385468</t>
+          <t>1385254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>30562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21583</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993874</t>
+          <t>994704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010533</t>
+          <t>1010815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998409</t>
+          <t>998411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1017292</t>
+          <t>1017057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2001491</t>
+          <t>1999499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2025338</t>
+          <t>2024428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740217</t>
+          <t>739906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752560</t>
+          <t>752594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760972</t>
+          <t>761886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772096</t>
+          <t>773007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505126</t>
+          <t>1506504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523266</t>
+          <t>1523219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935726</t>
+          <t>935472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945706</t>
+          <t>945702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027273</t>
+          <t>1028144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1043873</t>
+          <t>1043751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1970178</t>
+          <t>1969179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987477</t>
+          <t>1986803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55431</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68807</t>
+          <t>71483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,47 +2153,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>93968</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>76749</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>115093</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>93968</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>75815</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>116106</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3371348</t>
+          <t>3372003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3397017</t>
+          <t>3397553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3485183</t>
+          <t>3482507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3514796</t>
+          <t>3514694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,47 +2266,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6886801</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6865676</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6904020</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6886801</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6864663</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6904954</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2016</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655442</t>
+          <t>656217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668753</t>
+          <t>668915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646194</t>
+          <t>646161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663752</t>
+          <t>663362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1308165</t>
+          <t>1307789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1329350</t>
+          <t>1329268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46670</t>
+          <t>47982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999113</t>
+          <t>1000795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014804</t>
+          <t>1015012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012052</t>
+          <t>1011927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1030938</t>
+          <t>1031201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018674</t>
+          <t>2017362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041975</t>
+          <t>2041110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743052</t>
+          <t>742864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755404</t>
+          <t>755326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770177</t>
+          <t>769864</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781762</t>
+          <t>781878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1517657</t>
+          <t>1518234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1535730</t>
+          <t>1534977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35286</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918659</t>
+          <t>918424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931962</t>
+          <t>932055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020832</t>
+          <t>1020083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036099</t>
+          <t>1037022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946060</t>
+          <t>1943978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965981</t>
+          <t>1965255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75180</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123618</t>
+          <t>123584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3335122</t>
+          <t>3334661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3360416</t>
+          <t>3361652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3469362</t>
+          <t>3470241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3501387</t>
+          <t>3502063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6815274</t>
+          <t>6815308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6857345</t>
+          <t>6855183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1431-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683125</t>
+          <t>682199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>697265</t>
+          <t>696613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>678672</t>
+          <t>678180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>691140</t>
+          <t>691134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1366126</t>
+          <t>1366642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1385254</t>
+          <t>1385867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30562</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994704</t>
+          <t>995053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010815</t>
+          <t>1010864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998411</t>
+          <t>999855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1017057</t>
+          <t>1017148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999499</t>
+          <t>2001038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024428</t>
+          <t>2024423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739906</t>
+          <t>740099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752594</t>
+          <t>753304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>761886</t>
+          <t>761187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773007</t>
+          <t>772158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1506504</t>
+          <t>1506019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523219</t>
+          <t>1523410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935472</t>
+          <t>935178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945702</t>
+          <t>945691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028144</t>
+          <t>1028115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1043751</t>
+          <t>1044053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969179</t>
+          <t>1969177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1986803</t>
+          <t>1987420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71483</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3372003</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3397553</t>
+          <t>3397679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3482507</t>
+          <t>3485449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3514694</t>
+          <t>3514337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6865676</t>
+          <t>6864796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6904020</t>
+          <t>6904093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>39119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656217</t>
+          <t>656055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668915</t>
+          <t>668717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646161</t>
+          <t>646693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663362</t>
+          <t>663167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1307789</t>
+          <t>1308520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1329268</t>
+          <t>1329757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47982</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1000795</t>
+          <t>1000057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015012</t>
+          <t>1014212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1011927</t>
+          <t>1012413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1031201</t>
+          <t>1030859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2017362</t>
+          <t>2018783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041110</t>
+          <t>2042323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>742864</t>
+          <t>742736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755326</t>
+          <t>755274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>769864</t>
+          <t>769727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781878</t>
+          <t>782657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1518234</t>
+          <t>1518085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1534977</t>
+          <t>1534873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>36802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918424</t>
+          <t>917614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932055</t>
+          <t>931352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020083</t>
+          <t>1020722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037022</t>
+          <t>1036488</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1943978</t>
+          <t>1944544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965255</t>
+          <t>1965299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>75001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,42 +4100,42 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>102298</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>83455</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>123761</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>102298</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>83709</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>123584</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3334661</t>
+          <t>3332799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3361652</t>
+          <t>3360685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3470241</t>
+          <t>3469541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3502063</t>
+          <t>3501340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,47 +4213,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6836594</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6815131</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6855437</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>98,8%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6473</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6836594</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6815308</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6855183</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
         </is>
       </c>
     </row>
